--- a/reports/onprem_openshift_sizing.xlsx
+++ b/reports/onprem_openshift_sizing.xlsx
@@ -561,7 +561,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>On-Premise Infrastructure Metrics — HDFC — 09 Apr 2026</t>
+          <t>On-Premise Infrastructure Metrics — PNB — 13 Apr 2026</t>
         </is>
       </c>
     </row>
@@ -617,19 +617,19 @@
       </c>
       <c r="B4" s="7" t="n"/>
       <c r="C4" s="8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -647,19 +647,19 @@
       </c>
       <c r="B6" s="10" t="n"/>
       <c r="C6" s="11" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
@@ -670,19 +670,19 @@
       </c>
       <c r="B7" s="7" t="n"/>
       <c r="C7" s="8" t="n">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>43</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -700,19 +700,19 @@
       </c>
       <c r="B9" s="10" t="n"/>
       <c r="C9" s="11" t="n">
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>110</v>
+        <v>2310</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>121</v>
+        <v>2541</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>133</v>
+        <v>2795</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>146</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
@@ -723,19 +723,19 @@
       </c>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="8" t="n">
-        <v>100</v>
+        <v>5900</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>110</v>
+        <v>6490</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>121</v>
+        <v>7139</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>133</v>
+        <v>7852</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>146</v>
+        <v>8638</v>
       </c>
     </row>
   </sheetData>
@@ -1130,19 +1130,19 @@
       </c>
       <c r="F12" s="16" t="inlineStr"/>
       <c r="G12" s="16" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>240</v>
+        <v>488</v>
       </c>
       <c r="I12" s="16" t="n">
         <v>300</v>
       </c>
       <c r="J12" s="16" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>240</v>
+        <v>488</v>
       </c>
       <c r="L12" s="17" t="n">
         <v>0.29296875</v>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="D7" s="19" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
@@ -1688,13 +1688,13 @@
         <v>256</v>
       </c>
       <c r="J7" s="19" t="n">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>128</v>
+        <v>288</v>
       </c>
       <c r="L7" s="20" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="M7" s="19" t="n"/>
       <c r="N7" s="19" t="inlineStr"/>
@@ -1766,12 +1766,12 @@
       <c r="G10" s="19" t="n"/>
       <c r="H10" s="19" t="n"/>
       <c r="I10" s="19" t="n">
-        <v>3016</v>
+        <v>12096</v>
       </c>
       <c r="J10" s="19" t="n"/>
       <c r="K10" s="19" t="n"/>
       <c r="L10" s="20" t="n">
-        <v>2.9453125</v>
+        <v>11.8125</v>
       </c>
       <c r="M10" s="19" t="n"/>
       <c r="N10" s="19" t="inlineStr"/>
@@ -1807,19 +1807,19 @@
       </c>
       <c r="F12" s="16" t="inlineStr"/>
       <c r="G12" s="16" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>240</v>
+        <v>488</v>
       </c>
       <c r="I12" s="16" t="n">
         <v>300</v>
       </c>
       <c r="J12" s="16" t="n">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>480</v>
+        <v>976</v>
       </c>
       <c r="L12" s="17" t="n">
         <v>0.5859375</v>
@@ -1873,12 +1873,12 @@
       <c r="G14" s="16" t="n"/>
       <c r="H14" s="16" t="n"/>
       <c r="I14" s="16" t="n">
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="J14" s="16" t="n"/>
       <c r="K14" s="16" t="n"/>
       <c r="L14" s="17" t="n">
-        <v>0.1953125</v>
+        <v>4.1015625</v>
       </c>
       <c r="M14" s="16" t="n"/>
       <c r="N14" s="16" t="inlineStr"/>
@@ -1948,19 +1948,19 @@
       </c>
       <c r="F17" s="16" t="inlineStr"/>
       <c r="G17" s="16" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H17" s="16" t="n">
-        <v>240</v>
+        <v>488</v>
       </c>
       <c r="I17" s="16" t="n">
         <v>300</v>
       </c>
       <c r="J17" s="16" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K17" s="16" t="n">
-        <v>240</v>
+        <v>488</v>
       </c>
       <c r="L17" s="17" t="n">
         <v>0.29296875</v>
@@ -2014,12 +2014,12 @@
       <c r="G19" s="16" t="n"/>
       <c r="H19" s="16" t="n"/>
       <c r="I19" s="16" t="n">
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="J19" s="16" t="n"/>
       <c r="K19" s="16" t="n"/>
       <c r="L19" s="17" t="n">
-        <v>0.09765625</v>
+        <v>2.05078125</v>
       </c>
       <c r="M19" s="16" t="n"/>
       <c r="N19" s="16" t="inlineStr"/>
@@ -2061,12 +2061,12 @@
       <c r="G21" s="16" t="n"/>
       <c r="H21" s="16" t="n"/>
       <c r="I21" s="16" t="n">
-        <v>100</v>
+        <v>5900</v>
       </c>
       <c r="J21" s="16" t="n"/>
       <c r="K21" s="16" t="n"/>
       <c r="L21" s="17" t="n">
-        <v>0.09765625</v>
+        <v>5.76171875</v>
       </c>
       <c r="M21" s="16" t="n"/>
       <c r="N21" s="16" t="inlineStr"/>
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="D7" s="19" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
@@ -2533,13 +2533,13 @@
         <v>256</v>
       </c>
       <c r="J7" s="19" t="n">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>128</v>
+        <v>288</v>
       </c>
       <c r="L7" s="20" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="M7" s="19" t="n"/>
       <c r="N7" s="19" t="inlineStr"/>
@@ -2611,12 +2611,12 @@
       <c r="G10" s="19" t="n"/>
       <c r="H10" s="19" t="n"/>
       <c r="I10" s="19" t="n">
-        <v>3036</v>
+        <v>12896</v>
       </c>
       <c r="J10" s="19" t="n"/>
       <c r="K10" s="19" t="n"/>
       <c r="L10" s="20" t="n">
-        <v>2.96484375</v>
+        <v>12.59375</v>
       </c>
       <c r="M10" s="19" t="n"/>
       <c r="N10" s="19" t="inlineStr"/>
@@ -2652,19 +2652,19 @@
       </c>
       <c r="F12" s="16" t="inlineStr"/>
       <c r="G12" s="16" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>264</v>
+        <v>536</v>
       </c>
       <c r="I12" s="16" t="n">
         <v>300</v>
       </c>
       <c r="J12" s="16" t="n">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>528</v>
+        <v>1072</v>
       </c>
       <c r="L12" s="17" t="n">
         <v>0.5859375</v>
@@ -2718,12 +2718,12 @@
       <c r="G14" s="16" t="n"/>
       <c r="H14" s="16" t="n"/>
       <c r="I14" s="16" t="n">
-        <v>110</v>
+        <v>2310</v>
       </c>
       <c r="J14" s="16" t="n"/>
       <c r="K14" s="16" t="n"/>
       <c r="L14" s="17" t="n">
-        <v>0.21484375</v>
+        <v>4.51171875</v>
       </c>
       <c r="M14" s="16" t="n"/>
       <c r="N14" s="16" t="inlineStr"/>
@@ -2793,19 +2793,19 @@
       </c>
       <c r="F17" s="16" t="inlineStr"/>
       <c r="G17" s="16" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="H17" s="16" t="n">
-        <v>264</v>
+        <v>536</v>
       </c>
       <c r="I17" s="16" t="n">
         <v>300</v>
       </c>
       <c r="J17" s="16" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K17" s="16" t="n">
-        <v>264</v>
+        <v>536</v>
       </c>
       <c r="L17" s="17" t="n">
         <v>0.29296875</v>
@@ -2859,12 +2859,12 @@
       <c r="G19" s="16" t="n"/>
       <c r="H19" s="16" t="n"/>
       <c r="I19" s="16" t="n">
-        <v>110</v>
+        <v>2310</v>
       </c>
       <c r="J19" s="16" t="n"/>
       <c r="K19" s="16" t="n"/>
       <c r="L19" s="17" t="n">
-        <v>0.10742188</v>
+        <v>2.25585938</v>
       </c>
       <c r="M19" s="16" t="n"/>
       <c r="N19" s="16" t="inlineStr"/>
@@ -2906,12 +2906,12 @@
       <c r="G21" s="16" t="n"/>
       <c r="H21" s="16" t="n"/>
       <c r="I21" s="16" t="n">
-        <v>110</v>
+        <v>6490</v>
       </c>
       <c r="J21" s="16" t="n"/>
       <c r="K21" s="16" t="n"/>
       <c r="L21" s="17" t="n">
-        <v>0.10742188</v>
+        <v>6.33789062</v>
       </c>
       <c r="M21" s="16" t="n"/>
       <c r="N21" s="16" t="inlineStr"/>
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="D7" s="19" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
@@ -3378,13 +3378,13 @@
         <v>256</v>
       </c>
       <c r="J7" s="19" t="n">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>128</v>
+        <v>288</v>
       </c>
       <c r="L7" s="20" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="M7" s="19" t="n"/>
       <c r="N7" s="19" t="inlineStr"/>
@@ -3456,12 +3456,12 @@
       <c r="G10" s="19" t="n"/>
       <c r="H10" s="19" t="n"/>
       <c r="I10" s="19" t="n">
-        <v>3058</v>
+        <v>13776</v>
       </c>
       <c r="J10" s="19" t="n"/>
       <c r="K10" s="19" t="n"/>
       <c r="L10" s="20" t="n">
-        <v>2.98632812</v>
+        <v>13.453125</v>
       </c>
       <c r="M10" s="19" t="n"/>
       <c r="N10" s="19" t="inlineStr"/>
@@ -3497,19 +3497,19 @@
       </c>
       <c r="F12" s="16" t="inlineStr"/>
       <c r="G12" s="16" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>288</v>
+        <v>584</v>
       </c>
       <c r="I12" s="16" t="n">
         <v>300</v>
       </c>
       <c r="J12" s="16" t="n">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>576</v>
+        <v>1168</v>
       </c>
       <c r="L12" s="17" t="n">
         <v>0.5859375</v>
@@ -3563,12 +3563,12 @@
       <c r="G14" s="16" t="n"/>
       <c r="H14" s="16" t="n"/>
       <c r="I14" s="16" t="n">
-        <v>121</v>
+        <v>2541</v>
       </c>
       <c r="J14" s="16" t="n"/>
       <c r="K14" s="16" t="n"/>
       <c r="L14" s="17" t="n">
-        <v>0.23632812</v>
+        <v>4.96289062</v>
       </c>
       <c r="M14" s="16" t="n"/>
       <c r="N14" s="16" t="inlineStr"/>
@@ -3638,19 +3638,19 @@
       </c>
       <c r="F17" s="16" t="inlineStr"/>
       <c r="G17" s="16" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H17" s="16" t="n">
-        <v>288</v>
+        <v>584</v>
       </c>
       <c r="I17" s="16" t="n">
         <v>300</v>
       </c>
       <c r="J17" s="16" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="K17" s="16" t="n">
-        <v>288</v>
+        <v>584</v>
       </c>
       <c r="L17" s="17" t="n">
         <v>0.29296875</v>
@@ -3704,12 +3704,12 @@
       <c r="G19" s="16" t="n"/>
       <c r="H19" s="16" t="n"/>
       <c r="I19" s="16" t="n">
-        <v>121</v>
+        <v>2541</v>
       </c>
       <c r="J19" s="16" t="n"/>
       <c r="K19" s="16" t="n"/>
       <c r="L19" s="17" t="n">
-        <v>0.11816406</v>
+        <v>2.48144531</v>
       </c>
       <c r="M19" s="16" t="n"/>
       <c r="N19" s="16" t="inlineStr"/>
@@ -3751,12 +3751,12 @@
       <c r="G21" s="16" t="n"/>
       <c r="H21" s="16" t="n"/>
       <c r="I21" s="16" t="n">
-        <v>121</v>
+        <v>7139</v>
       </c>
       <c r="J21" s="16" t="n"/>
       <c r="K21" s="16" t="n"/>
       <c r="L21" s="17" t="n">
-        <v>0.11816406</v>
+        <v>6.97167969</v>
       </c>
       <c r="M21" s="16" t="n"/>
       <c r="N21" s="16" t="inlineStr"/>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="D7" s="19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
@@ -4223,13 +4223,13 @@
         <v>256</v>
       </c>
       <c r="J7" s="19" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>128</v>
+        <v>320</v>
       </c>
       <c r="L7" s="20" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="M7" s="19" t="n"/>
       <c r="N7" s="19" t="inlineStr"/>
@@ -4301,12 +4301,12 @@
       <c r="G10" s="19" t="n"/>
       <c r="H10" s="19" t="n"/>
       <c r="I10" s="19" t="n">
-        <v>3082</v>
+        <v>14999</v>
       </c>
       <c r="J10" s="19" t="n"/>
       <c r="K10" s="19" t="n"/>
       <c r="L10" s="20" t="n">
-        <v>3.00976562</v>
+        <v>14.64746094</v>
       </c>
       <c r="M10" s="19" t="n"/>
       <c r="N10" s="19" t="inlineStr"/>
@@ -4342,19 +4342,19 @@
       </c>
       <c r="F12" s="16" t="inlineStr"/>
       <c r="G12" s="16" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>312</v>
+        <v>648</v>
       </c>
       <c r="I12" s="16" t="n">
         <v>300</v>
       </c>
       <c r="J12" s="16" t="n">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>624</v>
+        <v>1296</v>
       </c>
       <c r="L12" s="17" t="n">
         <v>0.5859375</v>
@@ -4408,12 +4408,12 @@
       <c r="G14" s="16" t="n"/>
       <c r="H14" s="16" t="n"/>
       <c r="I14" s="16" t="n">
-        <v>133</v>
+        <v>2795</v>
       </c>
       <c r="J14" s="16" t="n"/>
       <c r="K14" s="16" t="n"/>
       <c r="L14" s="17" t="n">
-        <v>0.25976562</v>
+        <v>5.45898438</v>
       </c>
       <c r="M14" s="16" t="n"/>
       <c r="N14" s="16" t="inlineStr"/>
@@ -4483,19 +4483,19 @@
       </c>
       <c r="F17" s="16" t="inlineStr"/>
       <c r="G17" s="16" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="H17" s="16" t="n">
-        <v>312</v>
+        <v>648</v>
       </c>
       <c r="I17" s="16" t="n">
         <v>300</v>
       </c>
       <c r="J17" s="16" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="K17" s="16" t="n">
-        <v>312</v>
+        <v>648</v>
       </c>
       <c r="L17" s="17" t="n">
         <v>0.29296875</v>
@@ -4549,12 +4549,12 @@
       <c r="G19" s="16" t="n"/>
       <c r="H19" s="16" t="n"/>
       <c r="I19" s="16" t="n">
-        <v>133</v>
+        <v>2795</v>
       </c>
       <c r="J19" s="16" t="n"/>
       <c r="K19" s="16" t="n"/>
       <c r="L19" s="17" t="n">
-        <v>0.12988281</v>
+        <v>2.72949219</v>
       </c>
       <c r="M19" s="16" t="n"/>
       <c r="N19" s="16" t="inlineStr"/>
@@ -4596,12 +4596,12 @@
       <c r="G21" s="16" t="n"/>
       <c r="H21" s="16" t="n"/>
       <c r="I21" s="16" t="n">
-        <v>133</v>
+        <v>7852</v>
       </c>
       <c r="J21" s="16" t="n"/>
       <c r="K21" s="16" t="n"/>
       <c r="L21" s="17" t="n">
-        <v>0.12988281</v>
+        <v>7.66796875</v>
       </c>
       <c r="M21" s="16" t="n"/>
       <c r="N21" s="16" t="inlineStr"/>
@@ -5050,7 +5050,7 @@
         </is>
       </c>
       <c r="D7" s="19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
@@ -5068,13 +5068,13 @@
         <v>256</v>
       </c>
       <c r="J7" s="19" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>128</v>
+        <v>320</v>
       </c>
       <c r="L7" s="20" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="M7" s="19" t="n"/>
       <c r="N7" s="19" t="inlineStr"/>
@@ -5146,12 +5146,12 @@
       <c r="G10" s="19" t="n"/>
       <c r="H10" s="19" t="n"/>
       <c r="I10" s="19" t="n">
-        <v>3108</v>
+        <v>16064</v>
       </c>
       <c r="J10" s="19" t="n"/>
       <c r="K10" s="19" t="n"/>
       <c r="L10" s="20" t="n">
-        <v>3.03515625</v>
+        <v>15.6875</v>
       </c>
       <c r="M10" s="19" t="n"/>
       <c r="N10" s="19" t="inlineStr"/>
@@ -5187,19 +5187,19 @@
       </c>
       <c r="F12" s="16" t="inlineStr"/>
       <c r="G12" s="16" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>344</v>
+        <v>712</v>
       </c>
       <c r="I12" s="16" t="n">
         <v>300</v>
       </c>
       <c r="J12" s="16" t="n">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>688</v>
+        <v>1424</v>
       </c>
       <c r="L12" s="17" t="n">
         <v>0.5859375</v>
@@ -5253,12 +5253,12 @@
       <c r="G14" s="16" t="n"/>
       <c r="H14" s="16" t="n"/>
       <c r="I14" s="16" t="n">
-        <v>146</v>
+        <v>3074</v>
       </c>
       <c r="J14" s="16" t="n"/>
       <c r="K14" s="16" t="n"/>
       <c r="L14" s="17" t="n">
-        <v>0.28515625</v>
+        <v>6.00390625</v>
       </c>
       <c r="M14" s="16" t="n"/>
       <c r="N14" s="16" t="inlineStr"/>
@@ -5328,19 +5328,19 @@
       </c>
       <c r="F17" s="16" t="inlineStr"/>
       <c r="G17" s="16" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="H17" s="16" t="n">
-        <v>344</v>
+        <v>712</v>
       </c>
       <c r="I17" s="16" t="n">
         <v>300</v>
       </c>
       <c r="J17" s="16" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="K17" s="16" t="n">
-        <v>344</v>
+        <v>712</v>
       </c>
       <c r="L17" s="17" t="n">
         <v>0.29296875</v>
@@ -5394,12 +5394,12 @@
       <c r="G19" s="16" t="n"/>
       <c r="H19" s="16" t="n"/>
       <c r="I19" s="16" t="n">
-        <v>146</v>
+        <v>3074</v>
       </c>
       <c r="J19" s="16" t="n"/>
       <c r="K19" s="16" t="n"/>
       <c r="L19" s="17" t="n">
-        <v>0.14257812</v>
+        <v>3.00195312</v>
       </c>
       <c r="M19" s="16" t="n"/>
       <c r="N19" s="16" t="inlineStr"/>
@@ -5441,12 +5441,12 @@
       <c r="G21" s="16" t="n"/>
       <c r="H21" s="16" t="n"/>
       <c r="I21" s="16" t="n">
-        <v>146</v>
+        <v>8638</v>
       </c>
       <c r="J21" s="16" t="n"/>
       <c r="K21" s="16" t="n"/>
       <c r="L21" s="17" t="n">
-        <v>0.14257812</v>
+        <v>8.43554688</v>
       </c>
       <c r="M21" s="16" t="n"/>
       <c r="N21" s="16" t="inlineStr"/>
@@ -5895,7 +5895,7 @@
         </is>
       </c>
       <c r="D7" s="19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
@@ -5913,13 +5913,13 @@
         <v>256</v>
       </c>
       <c r="J7" s="19" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>128</v>
+        <v>320</v>
       </c>
       <c r="L7" s="20" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="M7" s="19" t="n"/>
       <c r="N7" s="19" t="inlineStr"/>
@@ -5991,12 +5991,12 @@
       <c r="G10" s="19" t="n"/>
       <c r="H10" s="19" t="n"/>
       <c r="I10" s="19" t="n">
-        <v>3108</v>
+        <v>16064</v>
       </c>
       <c r="J10" s="19" t="n"/>
       <c r="K10" s="19" t="n"/>
       <c r="L10" s="20" t="n">
-        <v>3.03515625</v>
+        <v>15.6875</v>
       </c>
       <c r="M10" s="19" t="n"/>
       <c r="N10" s="19" t="inlineStr"/>
@@ -6032,19 +6032,19 @@
       </c>
       <c r="F12" s="16" t="inlineStr"/>
       <c r="G12" s="16" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>344</v>
+        <v>712</v>
       </c>
       <c r="I12" s="16" t="n">
         <v>300</v>
       </c>
       <c r="J12" s="16" t="n">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>688</v>
+        <v>1424</v>
       </c>
       <c r="L12" s="17" t="n">
         <v>0.5859375</v>
@@ -6098,12 +6098,12 @@
       <c r="G14" s="16" t="n"/>
       <c r="H14" s="16" t="n"/>
       <c r="I14" s="16" t="n">
-        <v>146</v>
+        <v>3074</v>
       </c>
       <c r="J14" s="16" t="n"/>
       <c r="K14" s="16" t="n"/>
       <c r="L14" s="17" t="n">
-        <v>0.28515625</v>
+        <v>6.00390625</v>
       </c>
       <c r="M14" s="16" t="n"/>
       <c r="N14" s="16" t="inlineStr"/>
@@ -6173,19 +6173,19 @@
       </c>
       <c r="F17" s="16" t="inlineStr"/>
       <c r="G17" s="16" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="H17" s="16" t="n">
-        <v>344</v>
+        <v>712</v>
       </c>
       <c r="I17" s="16" t="n">
         <v>300</v>
       </c>
       <c r="J17" s="16" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="K17" s="16" t="n">
-        <v>344</v>
+        <v>712</v>
       </c>
       <c r="L17" s="17" t="n">
         <v>0.29296875</v>
@@ -6239,12 +6239,12 @@
       <c r="G19" s="16" t="n"/>
       <c r="H19" s="16" t="n"/>
       <c r="I19" s="16" t="n">
-        <v>146</v>
+        <v>3074</v>
       </c>
       <c r="J19" s="16" t="n"/>
       <c r="K19" s="16" t="n"/>
       <c r="L19" s="17" t="n">
-        <v>0.14257812</v>
+        <v>3.00195312</v>
       </c>
       <c r="M19" s="16" t="n"/>
       <c r="N19" s="16" t="inlineStr"/>
@@ -6286,12 +6286,12 @@
       <c r="G21" s="16" t="n"/>
       <c r="H21" s="16" t="n"/>
       <c r="I21" s="16" t="n">
-        <v>146</v>
+        <v>8638</v>
       </c>
       <c r="J21" s="16" t="n"/>
       <c r="K21" s="16" t="n"/>
       <c r="L21" s="17" t="n">
-        <v>0.14257812</v>
+        <v>8.43554688</v>
       </c>
       <c r="M21" s="16" t="n"/>
       <c r="N21" s="16" t="inlineStr"/>
@@ -6836,12 +6836,12 @@
       <c r="G10" s="19" t="n"/>
       <c r="H10" s="19" t="n"/>
       <c r="I10" s="19" t="n">
-        <v>1992</v>
+        <v>9792</v>
       </c>
       <c r="J10" s="19" t="n"/>
       <c r="K10" s="19" t="n"/>
       <c r="L10" s="20" t="n">
-        <v>1.9453125</v>
+        <v>9.5625</v>
       </c>
       <c r="M10" s="19" t="n"/>
       <c r="N10" s="19" t="inlineStr"/>
@@ -6877,19 +6877,19 @@
       </c>
       <c r="F12" s="16" t="inlineStr"/>
       <c r="G12" s="16" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>240</v>
+        <v>488</v>
       </c>
       <c r="I12" s="16" t="n">
         <v>300</v>
       </c>
       <c r="J12" s="16" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>240</v>
+        <v>488</v>
       </c>
       <c r="L12" s="17" t="n">
         <v>0.29296875</v>
@@ -6943,12 +6943,12 @@
       <c r="G14" s="16" t="n"/>
       <c r="H14" s="16" t="n"/>
       <c r="I14" s="16" t="n">
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="J14" s="16" t="n"/>
       <c r="K14" s="16" t="n"/>
       <c r="L14" s="17" t="n">
-        <v>0.09765625</v>
+        <v>2.05078125</v>
       </c>
       <c r="M14" s="16" t="n"/>
       <c r="N14" s="16" t="inlineStr"/>
@@ -6990,12 +6990,12 @@
       <c r="G16" s="16" t="n"/>
       <c r="H16" s="16" t="n"/>
       <c r="I16" s="16" t="n">
-        <v>100</v>
+        <v>5900</v>
       </c>
       <c r="J16" s="16" t="n"/>
       <c r="K16" s="16" t="n"/>
       <c r="L16" s="17" t="n">
-        <v>0.09765625</v>
+        <v>5.76171875</v>
       </c>
       <c r="M16" s="16" t="n"/>
       <c r="N16" s="16" t="inlineStr"/>
@@ -7554,19 +7554,19 @@
       </c>
       <c r="F12" s="16" t="inlineStr"/>
       <c r="G12" s="16" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>240</v>
+        <v>488</v>
       </c>
       <c r="I12" s="16" t="n">
         <v>300</v>
       </c>
       <c r="J12" s="16" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>240</v>
+        <v>488</v>
       </c>
       <c r="L12" s="17" t="n">
         <v>0.29296875</v>
